--- a/product_selector_out/STM32L4 series.xlsx
+++ b/product_selector_out/STM32L4 series.xlsx
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AW12" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX12" s="4" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AW13" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX13" s="4" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AW14" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX14" s="4" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="AW15" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX15" s="4" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AW16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX16" s="4" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="AW17" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX17" s="4" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AW18" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX18" s="4" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AW19" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX19" s="4" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="AW20" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX20" s="4" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="AW21" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX21" s="4" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="AW22" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX22" s="4" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="AW23" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX23" s="4" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="AW24" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX24" s="4" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="AW25" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX25" s="4" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="AW26" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX26" s="4" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="AW27" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX27" s="4" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AW28" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX28" s="4" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="AW29" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX29" s="4" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="AW30" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX30" s="4" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="AW31" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX31" s="4" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="AW32" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX32" s="4" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="AW33" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX33" s="4" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AW34" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX34" s="4" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="AW35" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX35" s="4" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="AW36" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX36" s="4" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="AW37" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX37" s="4" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="AW38" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX38" s="4" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="AW39" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX39" s="4" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="AW40" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX40" s="4" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="AW41" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX41" s="4" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="AW42" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX42" s="4" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="AW43" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX43" s="4" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="AW44" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX44" s="4" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="AW45" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX45" s="4" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="AW46" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX46" s="4" t="inlineStr">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="AW47" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX47" s="4" t="inlineStr">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="AW48" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX48" s="4" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="AW49" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX49" s="4" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="AW50" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX50" s="4" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="AW51" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX51" s="4" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="AW52" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX52" s="4" t="inlineStr">
@@ -14647,7 +14647,7 @@
       </c>
       <c r="AW53" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX53" s="4" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="AW54" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX54" s="4" t="inlineStr">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="AW55" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX55" s="4" t="inlineStr">
@@ -15628,7 +15628,7 @@
       </c>
       <c r="AW56" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX56" s="4" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="AW57" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX57" s="4" t="inlineStr">
@@ -16282,7 +16282,7 @@
       </c>
       <c r="AW58" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX58" s="4" t="inlineStr">
@@ -16609,7 +16609,7 @@
       </c>
       <c r="AW59" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX59" s="4" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="AW60" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX60" s="4" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="AW61" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX61" s="4" t="inlineStr">
@@ -17590,7 +17590,7 @@
       </c>
       <c r="AW62" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX62" s="4" t="inlineStr">
@@ -17917,7 +17917,7 @@
       </c>
       <c r="AW63" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX63" s="4" t="inlineStr">
@@ -18244,7 +18244,7 @@
       </c>
       <c r="AW64" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX64" s="4" t="inlineStr">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="AW65" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX65" s="4" t="inlineStr">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="AW66" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX66" s="4" t="inlineStr">
@@ -19225,7 +19225,7 @@
       </c>
       <c r="AW67" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX67" s="4" t="inlineStr">
@@ -19552,7 +19552,7 @@
       </c>
       <c r="AW68" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX68" s="4" t="inlineStr">
@@ -19879,7 +19879,7 @@
       </c>
       <c r="AW69" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX69" s="4" t="inlineStr">
@@ -20206,7 +20206,7 @@
       </c>
       <c r="AW70" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX70" s="4" t="inlineStr">
@@ -20533,7 +20533,7 @@
       </c>
       <c r="AW71" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX71" s="4" t="inlineStr">
@@ -20860,7 +20860,7 @@
       </c>
       <c r="AW72" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX72" s="4" t="inlineStr">
@@ -21187,7 +21187,7 @@
       </c>
       <c r="AW73" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX73" s="4" t="inlineStr">
@@ -21514,7 +21514,7 @@
       </c>
       <c r="AW74" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX74" s="4" t="inlineStr">
@@ -21841,7 +21841,7 @@
       </c>
       <c r="AW75" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX75" s="4" t="inlineStr">
@@ -21921,7 +21921,7 @@
       </c>
       <c r="BM75" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22168,7 +22168,7 @@
       </c>
       <c r="AW76" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX76" s="4" t="inlineStr">
@@ -22495,7 +22495,7 @@
       </c>
       <c r="AW77" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX77" s="4" t="inlineStr">
@@ -22822,7 +22822,7 @@
       </c>
       <c r="AW78" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX78" s="4" t="inlineStr">
@@ -23149,7 +23149,7 @@
       </c>
       <c r="AW79" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX79" s="4" t="inlineStr">
@@ -23476,7 +23476,7 @@
       </c>
       <c r="AW80" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX80" s="4" t="inlineStr">
@@ -23803,7 +23803,7 @@
       </c>
       <c r="AW81" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX81" s="4" t="inlineStr">
@@ -23883,7 +23883,7 @@
       </c>
       <c r="BM81" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -24130,7 +24130,7 @@
       </c>
       <c r="AW82" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX82" s="4" t="inlineStr">
@@ -24210,7 +24210,7 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -24457,7 +24457,7 @@
       </c>
       <c r="AW83" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX83" s="4" t="inlineStr">
@@ -24784,7 +24784,7 @@
       </c>
       <c r="AW84" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX84" s="4" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="BM84" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -25111,7 +25111,7 @@
       </c>
       <c r="AW85" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX85" s="4" t="inlineStr">
@@ -25438,7 +25438,7 @@
       </c>
       <c r="AW86" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX86" s="4" t="inlineStr">
@@ -25765,7 +25765,7 @@
       </c>
       <c r="AW87" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX87" s="4" t="inlineStr">
@@ -26092,7 +26092,7 @@
       </c>
       <c r="AW88" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX88" s="4" t="inlineStr">
@@ -26419,7 +26419,7 @@
       </c>
       <c r="AW89" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX89" s="4" t="inlineStr">
@@ -26746,7 +26746,7 @@
       </c>
       <c r="AW90" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX90" s="4" t="inlineStr">
@@ -27073,7 +27073,7 @@
       </c>
       <c r="AW91" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX91" s="4" t="inlineStr">
@@ -27400,7 +27400,7 @@
       </c>
       <c r="AW92" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX92" s="4" t="inlineStr">
@@ -27727,7 +27727,7 @@
       </c>
       <c r="AW93" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX93" s="4" t="inlineStr">
@@ -28054,7 +28054,7 @@
       </c>
       <c r="AW94" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX94" s="4" t="inlineStr">
@@ -28381,7 +28381,7 @@
       </c>
       <c r="AW95" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX95" s="4" t="inlineStr">
@@ -28708,7 +28708,7 @@
       </c>
       <c r="AW96" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX96" s="4" t="inlineStr">
@@ -29035,7 +29035,7 @@
       </c>
       <c r="AW97" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX97" s="4" t="inlineStr">
@@ -29362,7 +29362,7 @@
       </c>
       <c r="AW98" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX98" s="4" t="inlineStr">
@@ -29689,7 +29689,7 @@
       </c>
       <c r="AW99" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX99" s="4" t="inlineStr">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="AW100" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX100" s="4" t="inlineStr">
@@ -30343,7 +30343,7 @@
       </c>
       <c r="AW101" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX101" s="4" t="inlineStr">
@@ -30670,7 +30670,7 @@
       </c>
       <c r="AW102" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX102" s="4" t="inlineStr">
@@ -30997,7 +30997,7 @@
       </c>
       <c r="AW103" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX103" s="4" t="inlineStr">
@@ -31324,7 +31324,7 @@
       </c>
       <c r="AW104" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX104" s="4" t="inlineStr">
@@ -31651,7 +31651,7 @@
       </c>
       <c r="AW105" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX105" s="4" t="inlineStr">
@@ -32647,9 +32647,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX12" s="7" t="inlineStr">
@@ -32974,9 +32974,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX13" s="7" t="inlineStr">
@@ -33301,9 +33301,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX14" s="7" t="inlineStr">
@@ -33628,9 +33628,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX15" s="7" t="inlineStr">
@@ -33955,9 +33955,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX16" s="7" t="inlineStr">
@@ -34282,9 +34282,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX17" s="7" t="inlineStr">
@@ -34609,9 +34609,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX18" s="7" t="inlineStr">
@@ -34936,9 +34936,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX19" s="7" t="inlineStr">
@@ -35263,9 +35263,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX20" s="7" t="inlineStr">
@@ -35590,9 +35590,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX21" s="7" t="inlineStr">
@@ -35917,9 +35917,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX22" s="7" t="inlineStr">
@@ -36244,9 +36244,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX23" s="7" t="inlineStr">
@@ -36571,9 +36571,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX24" s="7" t="inlineStr">
@@ -36898,9 +36898,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX25" s="7" t="inlineStr">
@@ -37225,9 +37225,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX26" s="7" t="inlineStr">
@@ -37552,9 +37552,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX27" s="7" t="inlineStr">
@@ -37879,9 +37879,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX28" s="7" t="inlineStr">
@@ -38206,9 +38206,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX29" s="7" t="inlineStr">
@@ -38533,9 +38533,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX30" s="7" t="inlineStr">
@@ -38860,9 +38860,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX31" s="7" t="inlineStr">
@@ -39187,9 +39187,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW32" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX32" s="7" t="inlineStr">
@@ -39514,9 +39514,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX33" s="7" t="inlineStr">
@@ -39841,9 +39841,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX34" s="7" t="inlineStr">
@@ -40168,9 +40168,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX35" s="7" t="inlineStr">
@@ -40495,9 +40495,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW36" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX36" s="7" t="inlineStr">
@@ -40822,9 +40822,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW37" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX37" s="7" t="inlineStr">
@@ -41149,9 +41149,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW38" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX38" s="7" t="inlineStr">
@@ -41476,9 +41476,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW39" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX39" s="7" t="inlineStr">
@@ -41803,9 +41803,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX40" s="7" t="inlineStr">
@@ -42130,9 +42130,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW41" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX41" s="7" t="inlineStr">
@@ -42457,9 +42457,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX42" s="7" t="inlineStr">
@@ -42784,9 +42784,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX43" s="7" t="inlineStr">
@@ -43111,9 +43111,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX44" s="7" t="inlineStr">
@@ -43438,9 +43438,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW45" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW45" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX45" s="7" t="inlineStr">
@@ -43765,9 +43765,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW46" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW46" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX46" s="7" t="inlineStr">
@@ -44092,9 +44092,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW47" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW47" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX47" s="7" t="inlineStr">
@@ -44419,9 +44419,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW48" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW48" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX48" s="7" t="inlineStr">
@@ -44746,9 +44746,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW49" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW49" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX49" s="7" t="inlineStr">
@@ -45073,9 +45073,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW50" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW50" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX50" s="7" t="inlineStr">
@@ -45400,9 +45400,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW51" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW51" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX51" s="7" t="inlineStr">
@@ -45727,9 +45727,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW52" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW52" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX52" s="7" t="inlineStr">
@@ -46054,9 +46054,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW53" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW53" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX53" s="7" t="inlineStr">
@@ -46381,9 +46381,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW54" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX54" s="7" t="inlineStr">
@@ -46708,9 +46708,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW55" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW55" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX55" s="7" t="inlineStr">
@@ -47035,9 +47035,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW56" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX56" s="7" t="inlineStr">
@@ -47362,9 +47362,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW57" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW57" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX57" s="7" t="inlineStr">
@@ -47689,9 +47689,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW58" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW58" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX58" s="7" t="inlineStr">
@@ -48016,9 +48016,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW59" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW59" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX59" s="7" t="inlineStr">
@@ -48343,9 +48343,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW60" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW60" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX60" s="7" t="inlineStr">
@@ -48670,9 +48670,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW61" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW61" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX61" s="7" t="inlineStr">
@@ -48997,9 +48997,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW62" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW62" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX62" s="7" t="inlineStr">
@@ -49324,9 +49324,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW63" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW63" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX63" s="7" t="inlineStr">
@@ -49651,9 +49651,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX64" s="7" t="inlineStr">
@@ -49978,9 +49978,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW65" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX65" s="7" t="inlineStr">
@@ -50305,9 +50305,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW66" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW66" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX66" s="7" t="inlineStr">
@@ -50632,9 +50632,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW67" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX67" s="7" t="inlineStr">
@@ -50959,9 +50959,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX68" s="7" t="inlineStr">
@@ -51286,9 +51286,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW69" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW69" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX69" s="7" t="inlineStr">
@@ -51613,9 +51613,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW70" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW70" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX70" s="7" t="inlineStr">
@@ -51940,9 +51940,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW71" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX71" s="7" t="inlineStr">
@@ -52267,9 +52267,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW72" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX72" s="7" t="inlineStr">
@@ -52594,9 +52594,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW73" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW73" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX73" s="7" t="inlineStr">
@@ -52921,9 +52921,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW74" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX74" s="7" t="inlineStr">
@@ -53028,9 +53028,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
@@ -53093,14 +53093,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R75" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S75" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R75" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S75" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T75" s="6" t="inlineStr">
@@ -53248,14 +53248,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW75" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX75" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW75" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX75" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY75" s="6" t="inlineStr">
@@ -53328,9 +53328,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM75" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -53575,9 +53575,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW76" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW76" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX76" s="7" t="inlineStr">
@@ -53902,9 +53902,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW77" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW77" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX77" s="7" t="inlineStr">
@@ -54229,9 +54229,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW78" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW78" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX78" s="7" t="inlineStr">
@@ -54556,9 +54556,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW79" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW79" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX79" s="7" t="inlineStr">
@@ -54883,9 +54883,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW80" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW80" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX80" s="7" t="inlineStr">
@@ -54990,9 +54990,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
@@ -55055,14 +55055,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R81" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S81" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R81" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S81" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T81" s="6" t="inlineStr">
@@ -55210,14 +55210,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW81" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX81" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW81" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX81" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY81" s="6" t="inlineStr">
@@ -55290,9 +55290,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM81" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -55317,9 +55317,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
@@ -55382,14 +55382,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R82" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S82" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T82" s="6" t="inlineStr">
@@ -55537,14 +55537,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW82" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX82" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY82" s="6" t="inlineStr">
@@ -55617,9 +55617,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM82" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -55864,9 +55864,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW83" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW83" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX83" s="7" t="inlineStr">
@@ -55971,9 +55971,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -56036,14 +56036,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R84" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S84" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T84" s="6" t="inlineStr">
@@ -56191,14 +56191,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY84" s="6" t="inlineStr">
@@ -56271,9 +56271,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM84" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -56518,9 +56518,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW85" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW85" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX85" s="7" t="inlineStr">
@@ -56845,9 +56845,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW86" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX86" s="7" t="inlineStr">
@@ -57172,9 +57172,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW87" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX87" s="7" t="inlineStr">
@@ -57499,9 +57499,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW88" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW88" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX88" s="7" t="inlineStr">
@@ -57826,9 +57826,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW89" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW89" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX89" s="7" t="inlineStr">
@@ -58153,9 +58153,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW90" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW90" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX90" s="7" t="inlineStr">
@@ -58480,9 +58480,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW91" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW91" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX91" s="7" t="inlineStr">
@@ -58807,9 +58807,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW92" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW92" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX92" s="7" t="inlineStr">
@@ -59134,9 +59134,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW93" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW93" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX93" s="7" t="inlineStr">
@@ -59461,9 +59461,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW94" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW94" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX94" s="7" t="inlineStr">
@@ -59788,9 +59788,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW95" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW95" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX95" s="7" t="inlineStr">
@@ -60115,9 +60115,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW96" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW96" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX96" s="7" t="inlineStr">
@@ -60442,9 +60442,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW97" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW97" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX97" s="7" t="inlineStr">
@@ -60769,9 +60769,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW98" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW98" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX98" s="7" t="inlineStr">
@@ -61096,9 +61096,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW99" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW99" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX99" s="7" t="inlineStr">
@@ -61423,9 +61423,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW100" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW100" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX100" s="7" t="inlineStr">
@@ -61750,9 +61750,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW101" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW101" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX101" s="7" t="inlineStr">
@@ -62077,9 +62077,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW102" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW102" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX102" s="7" t="inlineStr">
@@ -62404,9 +62404,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW103" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW103" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX103" s="7" t="inlineStr">
@@ -62731,9 +62731,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW104" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW104" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX104" s="7" t="inlineStr">
@@ -63058,9 +63058,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW105" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW105" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX105" s="7" t="inlineStr">
@@ -63159,7 +63159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D274"/>
+  <dimension ref="A1:D356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -63237,12 +63237,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32L412KB</t>
+          <t>STM32L442KC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -63252,7 +63252,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -63264,7 +63264,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -63281,12 +63281,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32L422KB</t>
+          <t>STM32L412KB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -63296,19 +63296,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32L422KB</t>
+          <t>STM32L412KB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -63318,7 +63318,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -63330,7 +63330,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -63340,19 +63340,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32L462CE</t>
+          <t>STM32L422KB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -63362,19 +63362,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 1. STM32L462xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32L462CE</t>
+          <t>STM32L422KB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -63384,19 +63384,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32L462CE</t>
+          <t>STM32L422KB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -63406,7 +63406,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -63418,7 +63418,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -63428,7 +63428,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 1. STM32L462xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
@@ -63440,7 +63440,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -63450,19 +63450,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32L412C8</t>
+          <t>STM32L462CE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -63472,19 +63472,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32L412C8</t>
+          <t>STM32L462CE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -63494,19 +63494,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32L412R8</t>
+          <t>STM32L462CE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -63516,19 +63516,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32L412R8</t>
+          <t>STM32L462CE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -63538,14 +63538,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32L412T8</t>
+          <t>STM32L412C8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -63567,7 +63567,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32L412T8</t>
+          <t>STM32L412C8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -63589,12 +63589,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L412C8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -63604,14 +63604,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 1. STM32L462xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L412R8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -63626,14 +63626,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L412R8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -63648,19 +63648,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L412R8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -63670,19 +63670,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L462RE</t>
+          <t>STM32L412T8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -63692,19 +63692,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L412T8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -63714,19 +63714,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L412T8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -63736,19 +63736,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -63758,19 +63758,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 1. STM32L462xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -63780,19 +63780,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L452RE</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -63802,19 +63802,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -63824,19 +63824,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 1. STM32L432Kx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -63846,14 +63846,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 1. STM32L432Kx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32L432KB</t>
+          <t>STM32L462RE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -63868,14 +63868,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / - 40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -63890,14 +63890,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -63919,7 +63919,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -63941,7 +63941,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -63963,12 +63963,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L452VE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -63978,19 +63978,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L452RE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -64000,19 +64000,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 1. STM32L462xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -64022,19 +64022,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 1. STM32L432Kx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -64044,19 +64044,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 1. STM32L432Kx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -64066,14 +64066,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32L462VE</t>
+          <t>STM32L432KB</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -64088,14 +64088,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Ambient operating temperature: -40 to 85 °C / - 40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -64110,19 +64110,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -64132,19 +64132,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L422CB</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -64154,19 +64154,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -64176,19 +64176,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -64198,19 +64198,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L452VE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -64220,19 +64220,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -64242,19 +64242,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 1. STM32L462xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32L452CE</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -64264,19 +64264,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -64286,14 +64286,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -64308,19 +64308,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 1. STM32L462xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32L422RB</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -64330,19 +64330,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32L412RB</t>
+          <t>STM32L462VE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -64352,19 +64352,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32L412RB</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -64374,19 +64374,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -64396,19 +64396,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -64418,19 +64418,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L422CB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -64440,19 +64440,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -64462,19 +64462,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L452CC</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -64484,19 +64484,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L412K8</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -64506,19 +64506,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32L412K8</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -64528,19 +64528,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32L412TB</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -64550,19 +64550,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L412TB</t>
+          <t>STM32L452CE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -64572,14 +64572,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -64594,14 +64594,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 1. STM32L432Kx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -64616,19 +64616,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 1. STM32L432Kx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L432KC</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -64638,19 +64638,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / - 40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L422RB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -64660,14 +64660,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L412RB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -64682,14 +64682,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L412RB</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -64704,19 +64704,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L412RB</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -64726,19 +64726,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32L452RC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -64748,19 +64748,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -64770,19 +64770,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -64799,12 +64799,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -64814,19 +64814,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -64836,14 +64836,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32L452VC</t>
+          <t>STM32L452CC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -64865,7 +64865,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32L412CB</t>
+          <t>STM32L412K8</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -64887,7 +64887,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32L412CB</t>
+          <t>STM32L412K8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -64909,12 +64909,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32L422TB</t>
+          <t>STM32L412K8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -64924,19 +64924,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts lists WLCSP36 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32L422TB</t>
+          <t>STM32L412TB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -64946,19 +64946,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32L422TB</t>
+          <t>STM32L412TB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -64968,19 +64968,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32L443RC</t>
+          <t>STM32L412TB</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -64990,19 +64990,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 1. STM32L443xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32L443RC</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -65012,19 +65012,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 1. STM32L443xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 1. STM32L432Kx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32L443RC</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -65034,19 +65034,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 1. STM32L432Kx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32L443VC</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -65056,19 +65056,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 1. STM32L443xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32L443VC</t>
+          <t>STM32L432KC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -65078,19 +65078,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 1. STM32L443xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / - 40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32L443VC</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -65100,19 +65100,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -65122,19 +65122,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -65144,19 +65144,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32L433VC</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -65166,19 +65166,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -65188,19 +65188,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L452RC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -65210,19 +65210,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32L433CB</t>
+          <t>STM32L452VC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -65232,19 +65232,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L452VC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -65254,19 +65254,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L452VC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -65276,19 +65276,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32L433RB</t>
+          <t>STM32L452VC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -65298,19 +65298,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L452xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L452VC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -65320,19 +65320,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Table 1. STM32L443xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L452VC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -65342,19 +65342,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Table 1. STM32L443xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32L443CC</t>
+          <t>STM32L412CB</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -65364,19 +65364,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L412CB</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -65386,19 +65386,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L412CB</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -65408,19 +65408,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32L433CC</t>
+          <t>STM32L422TB</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -65430,19 +65430,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts lists WLCSP36 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32L433RC</t>
+          <t>STM32L422TB</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -65452,19 +65452,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L422xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32L433RC</t>
+          <t>STM32L422TB</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -65474,14 +65474,14 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32L433RC</t>
+          <t>STM32L422TB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -65496,14 +65496,14 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32L475VC</t>
+          <t>STM32L443RC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -65518,14 +65518,14 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 1. STM32L443xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32L475VC</t>
+          <t>STM32L443RC</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -65540,19 +65540,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 1. STM32L443xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32L475VC</t>
+          <t>STM32L443RC</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -65562,19 +65562,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32L475RE</t>
+          <t>STM32L443RC</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -65584,19 +65584,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32L475RE</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -65606,19 +65606,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 1. STM32L443xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32L475RE</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -65628,19 +65628,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 1. STM32L443xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32L475VG</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -65650,19 +65650,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32L475VG</t>
+          <t>STM32L443VC</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -65672,19 +65672,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32L475VG</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -65694,19 +65694,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32L475VE</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -65716,19 +65716,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32L475VE</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -65738,14 +65738,14 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32L475VE</t>
+          <t>STM32L433VC</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -65767,7 +65767,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32L475RC</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -65782,14 +65782,14 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32L475RC</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -65804,19 +65804,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32L475RC</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -65826,19 +65826,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32L475RG</t>
+          <t>STM32L433CB</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -65848,19 +65848,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32L475RG</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -65870,19 +65870,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32L475RG</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -65892,19 +65892,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32L451VC</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -65914,19 +65914,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32L451VC</t>
+          <t>STM32L433RB</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -65936,19 +65936,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32L451VC</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -65958,14 +65958,14 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 1. STM32L443xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32L451VC</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -65980,19 +65980,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 1. STM32L443xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32L451VC</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -66002,19 +66002,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32L471RG</t>
+          <t>STM32L443CC</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -66024,19 +66024,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32L471RG</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -66046,19 +66046,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32L471RG</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -66068,19 +66068,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32L451RC</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -66090,19 +66090,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32L451RC</t>
+          <t>STM32L433CC</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -66112,19 +66112,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32L451RC</t>
+          <t>STM32L433RC</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -66134,14 +66134,14 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L433xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32L451RC</t>
+          <t>STM32L433RC</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -66156,19 +66156,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L433xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32L451RC</t>
+          <t>STM32L433RC</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -66178,19 +66178,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32L471VG</t>
+          <t>STM32L433RC</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -66200,19 +66200,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32L471VG</t>
+          <t>STM32L475VC</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -66222,19 +66222,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32L471VG</t>
+          <t>STM32L475VC</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -66244,19 +66244,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32L471VE</t>
+          <t>STM32L475VC</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -66266,19 +66266,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32L471VE</t>
+          <t>STM32L475VC</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -66288,19 +66288,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32L471VE</t>
+          <t>STM32L475RE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -66310,19 +66310,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L475RE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -66332,19 +66332,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L475RE</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -66354,19 +66354,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L475RE</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -66376,19 +66376,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L475VG</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -66398,19 +66398,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32L451CC</t>
+          <t>STM32L475VG</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -66420,19 +66420,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L475VG</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -66442,19 +66442,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L475VG</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -66464,19 +66464,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L475VE</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -66486,14 +66486,14 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L475VE</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -66508,19 +66508,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32L451VE</t>
+          <t>STM32L475VE</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -66530,19 +66530,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32L471RE</t>
+          <t>STM32L475VE</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -66552,19 +66552,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32L471RE</t>
+          <t>STM32L475RC</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -66574,19 +66574,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32L471RE</t>
+          <t>STM32L475RC</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -66596,19 +66596,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L475RC</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -66618,19 +66618,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L475RC</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -66640,19 +66640,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32L431RC</t>
+          <t>STM32L475RG</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -66662,19 +66662,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L475RG</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -66684,19 +66684,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L475xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L475RG</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -66706,19 +66706,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L475RG</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -66728,19 +66728,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L451VC</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -66750,19 +66750,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32L451RE</t>
+          <t>STM32L451VC</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -66772,19 +66772,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L451VC</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -66794,14 +66794,14 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L451VC</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -66816,19 +66816,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32L471QG</t>
+          <t>STM32L451VC</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -66838,19 +66838,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L451VC</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -66860,19 +66860,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L471RG</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -66882,19 +66882,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>STM32L431CC</t>
+          <t>STM32L471RG</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -66904,19 +66904,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L471RG</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -66926,19 +66926,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L471RG</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -66948,19 +66948,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32L431RB</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -66970,19 +66970,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -66992,19 +66992,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -67021,12 +67021,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -67036,19 +67036,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -67058,14 +67058,14 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STM32L451CE</t>
+          <t>STM32L451RC</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -67087,7 +67087,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -67102,14 +67102,14 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -67131,12 +67131,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>STM32L471QE</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -67146,19 +67146,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L471VG</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -67168,19 +67168,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -67190,19 +67190,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STM32L471ZE</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -67212,19 +67212,19 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -67234,19 +67234,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L471VE</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -67256,19 +67256,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>STM32L431CB</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -67278,19 +67278,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -67300,19 +67300,19 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -67322,19 +67322,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>STM32L431KC</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -67344,19 +67344,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -67366,19 +67366,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L451CC</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -67388,19 +67388,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>STM32L471ZG</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -67410,19 +67410,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -67432,19 +67432,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -67454,19 +67454,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>STM32L431KB</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -67476,19 +67476,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>STM32L431VC</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -67498,19 +67498,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>STM32L431VC</t>
+          <t>STM32L451VE</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -67520,19 +67520,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>STM32L431VC</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -67542,19 +67542,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>STM32L476JE</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -67564,19 +67564,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>STM32L476JE</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -67586,19 +67586,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>STM32L476RC</t>
+          <t>STM32L471RE</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -67608,19 +67608,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>STM32L476RC</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -67630,19 +67630,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>STM32L4A6AG</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -67652,19 +67652,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>STM32L4A6AG</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -67674,19 +67674,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>STM32L486ZG</t>
+          <t>STM32L431RC</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -67696,19 +67696,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>STM32L486ZG</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -67718,19 +67718,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>STM32L486ZG</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -67740,19 +67740,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>STM32L4A6ZG</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -67762,19 +67762,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>STM32L4A6ZG</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -67784,19 +67784,19 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>STM32L476JG</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -67806,19 +67806,19 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>STM32L476JG</t>
+          <t>STM32L451RE</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -67828,14 +67828,14 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>STM32L486QG</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -67850,14 +67850,14 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>STM32L486QG</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -67872,19 +67872,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>STM32L486QG</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -67894,19 +67894,19 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>STM32L496QE</t>
+          <t>STM32L471QG</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -67916,19 +67916,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>STM32L496QE</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -67938,19 +67938,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>STM32L486JG</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -67960,19 +67960,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists WLCSP72 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>STM32L486JG</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -67982,14 +67982,14 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>STM32L486JG</t>
+          <t>STM32L431CC</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -68011,7 +68011,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>STM32L486VG</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -68026,14 +68026,14 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP64, UFBGA64, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>STM32L486VG</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -68048,19 +68048,19 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>STM32L486VG</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -68070,19 +68070,19 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>STM32L4A6QG</t>
+          <t>STM32L431RB</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -68092,19 +68092,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>STM32L4A6QG</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -68114,14 +68114,14 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>STM32L4A6VG</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -68136,14 +68136,14 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>STM32L4A6VG</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -68158,19 +68158,19 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison lists the family's timers, but this variant's counts differ (basic: summary 2, inventory 1), and the table does not say which timers the variant omits</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>STM32L476VC</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -68180,19 +68180,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L451xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>STM32L476VC</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -68202,19 +68202,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>STM32L4A6RG</t>
+          <t>STM32L451CE</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -68224,19 +68224,19 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>STM32L4A6RG</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -68246,19 +68246,19 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>STM32L476QG</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -68268,19 +68268,19 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>STM32L476QG</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -68290,19 +68290,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>STM32L496VE</t>
+          <t>STM32L471QE</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -68312,19 +68312,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>STM32L496VE</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -68334,19 +68334,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>STM32L476VG</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -68356,19 +68356,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>STM32L476VG</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -68378,19 +68378,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>STM32L496RE</t>
+          <t>STM32L471ZE</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -68400,19 +68400,19 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>STM32L496RE</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -68422,19 +68422,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>STM32L476RG</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -68444,19 +68444,19 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>STM32L476RG</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -68466,19 +68466,19 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>STM32L496AE</t>
+          <t>STM32L431CB</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -68488,19 +68488,19 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>STM32L496AE</t>
+          <t>STM32L431KC</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -68510,19 +68510,19 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>STM32L496ZE</t>
+          <t>STM32L431KC</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -68532,19 +68532,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>STM32L496ZE</t>
+          <t>STM32L431KC</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -68554,19 +68554,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>STM32L476ZE</t>
+          <t>STM32L431KC</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -68576,19 +68576,19 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>STM32L476ZE</t>
+          <t>STM32L471ZG</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -68598,19 +68598,19 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts lists LQFP144, UFBGA144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>STM32L476ZG</t>
+          <t>STM32L471ZG</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -68620,19 +68620,19 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L471xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>STM32L476ZG</t>
+          <t>STM32L471ZG</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -68642,19 +68642,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>STM32L496VG</t>
+          <t>STM32L471ZG</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -68664,19 +68664,19 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>STM32L496VG</t>
+          <t>STM32L431KB</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -68686,19 +68686,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>STM32L496QG</t>
+          <t>STM32L431KB</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -68708,19 +68708,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>STM32L496QG</t>
+          <t>STM32L431KB</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -68730,19 +68730,19 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>STM32L476MG</t>
+          <t>STM32L431KB</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -68752,19 +68752,19 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>STM32L476MG</t>
+          <t>STM32L431VC</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -68774,19 +68774,19 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts lists LQFP100, UFBGA100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>STM32L496AG</t>
+          <t>STM32L431VC</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -68796,19 +68796,19 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L431xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>STM32L496AG</t>
+          <t>STM32L431VC</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -68818,19 +68818,19 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>STM32L476QE</t>
+          <t>STM32L431VC</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -68840,19 +68840,19 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>STM32L476QE</t>
+          <t>STM32L476JE</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -68869,12 +68869,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>STM32L476VE</t>
+          <t>STM32L476JE</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -68891,12 +68891,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>STM32L476VE</t>
+          <t>STM32L476JE</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -68906,14 +68906,14 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>STM32L476RE</t>
+          <t>STM32L476RC</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -68935,7 +68935,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>STM32L476RE</t>
+          <t>STM32L476RC</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -68957,12 +68957,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>STM32L496RG</t>
+          <t>STM32L476RC</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -68972,19 +68972,19 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>STM32L496RG</t>
+          <t>STM32L4A6AG</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -69001,12 +69001,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>STM32L496ZG</t>
+          <t>STM32L4A6AG</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -69023,12 +69023,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>STM32L496ZG</t>
+          <t>STM32L4A6AG</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -69038,19 +69038,19 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>STM32L476ME</t>
+          <t>STM32L486ZG</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -69060,19 +69060,19 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP144 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>STM32L476ME</t>
+          <t>STM32L486ZG</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -69082,19 +69082,19 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L486ZG</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -69104,19 +69104,19 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L486ZG</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -69126,19 +69126,19 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L476JG</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -69148,19 +69148,19 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>STM32L496WG</t>
+          <t>STM32L476JG</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -69170,29 +69170,1833 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
+          <t>STM32L476JG</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>STM32L486QG</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>STM32L486QG</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>STM32L486QG</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>STM32L486QG</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>STM32L496QE</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>STM32L496QE</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>STM32L496QE</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>STM32L486JG</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists WLCSP72 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>STM32L486JG</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>STM32L486JG</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>STM32L486JG</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>STM32L486VG</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>STM32L486VG</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>STM32L486VG</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>STM32L486VG</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>STM32L476VC</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>STM32L476VC</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>STM32L476VC</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>STM32L476QG</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>STM32L476QG</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>STM32L476QG</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>STM32L496VE</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>STM32L496VE</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>STM32L496VE</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>STM32L476VG</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>STM32L476VG</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>STM32L476VG</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>STM32L496RE</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>STM32L496RE</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>STM32L496RE</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>STM32L476RG</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>STM32L476RG</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>STM32L476RG</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>STM32L496AE</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>STM32L496AE</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>STM32L496AE</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>STM32L496ZE</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>STM32L496ZE</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>STM32L496ZE</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>STM32L476ZE</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>STM32L476ZE</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>STM32L476ZE</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>STM32L476ZG</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>STM32L476ZG</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>STM32L476ZG</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>STM32L496VG</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>STM32L496VG</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>STM32L496VG</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>STM32L496QG</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>STM32L496QG</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>STM32L496QG</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>STM32L476MG</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>STM32L476MG</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>STM32L476MG</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>STM32L496AG</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>STM32L496AG</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>STM32L496AG</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>STM32L476QE</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>STM32L476QE</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>STM32L476QE</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>STM32L476VE</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>STM32L476VE</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>STM32L476VE</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>STM32L476RE</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>STM32L476RE</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>STM32L476RE</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>STM32L496RG</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>STM32L496RG</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>STM32L496RG</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>STM32L496ZG</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>STM32L496ZG</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>STM32L496ZG</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>STM32L476ME</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>STM32L476ME</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>STM32L476ME</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
           <t>STM32L496WG</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>STM32L496WG</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
         <is>
           <t>Timers (32-bit) typ</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
+      <c r="C355" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr">
+      <c r="D355" t="inlineStr">
         <is>
           <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>STM32L496WG</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32L4 series.xlsx
+++ b/product_selector_out/STM32L4 series.xlsx
@@ -21921,7 +21921,7 @@
       </c>
       <c r="BM75" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
     </row>
@@ -23883,7 +23883,7 @@
       </c>
       <c r="BM81" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
     </row>
@@ -24210,7 +24210,7 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
     </row>
@@ -24864,7 +24864,7 @@
       </c>
       <c r="BM84" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
     </row>
@@ -53028,9 +53028,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
@@ -53093,14 +53093,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R75" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S75" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R75" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S75" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T75" s="6" t="inlineStr">
@@ -53248,14 +53248,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW75" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX75" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW75" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX75" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY75" s="6" t="inlineStr">
@@ -53328,9 +53328,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM75" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM75" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -54990,9 +54990,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
@@ -55055,14 +55055,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R81" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S81" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T81" s="6" t="inlineStr">
@@ -55210,14 +55210,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW81" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX81" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY81" s="6" t="inlineStr">
@@ -55290,9 +55290,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM81" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM81" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -55317,9 +55317,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
@@ -55382,14 +55382,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R82" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S82" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T82" s="6" t="inlineStr">
@@ -55537,14 +55537,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW82" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX82" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY82" s="6" t="inlineStr">
@@ -55617,9 +55617,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -55971,9 +55971,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -56036,14 +56036,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R84" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S84" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T84" s="6" t="inlineStr">
@@ -56191,14 +56191,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW84" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX84" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY84" s="6" t="inlineStr">
@@ -56271,9 +56271,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM84" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -63159,7 +63159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D356"/>
+  <dimension ref="A1:D368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -69133,7 +69133,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>STM32L476JG</t>
+          <t>STM32L4A6ZG</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -69148,14 +69148,14 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>STM32L476JG</t>
+          <t>STM32L4A6ZG</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -69170,14 +69170,14 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>STM32L476JG</t>
+          <t>STM32L4A6ZG</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -69192,19 +69192,19 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>STM32L486QG</t>
+          <t>STM32L476JG</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -69214,19 +69214,19 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>STM32L486QG</t>
+          <t>STM32L476JG</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -69236,14 +69236,14 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>STM32L486QG</t>
+          <t>STM32L476JG</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -69270,7 +69270,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -69280,19 +69280,19 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists UFBGA132 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>STM32L496QE</t>
+          <t>STM32L486QG</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -69302,19 +69302,19 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>STM32L496QE</t>
+          <t>STM32L486QG</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -69324,19 +69324,19 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>STM32L496QE</t>
+          <t>STM32L486QG</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -69346,19 +69346,19 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>STM32L486JG</t>
+          <t>STM32L496QE</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -69368,19 +69368,19 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists WLCSP72 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>STM32L486JG</t>
+          <t>STM32L496QE</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -69390,14 +69390,14 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>STM32L486JG</t>
+          <t>STM32L496QE</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -69412,7 +69412,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -69424,7 +69424,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -69434,19 +69434,19 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists WLCSP72 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>STM32L486VG</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -69456,19 +69456,19 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>STM32L486VG</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -69478,19 +69478,19 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>STM32L486VG</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -69500,7 +69500,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -69512,7 +69512,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -69522,19 +69522,19 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>STM32L476VC</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -69544,19 +69544,19 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>STM32L476VC</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -69566,19 +69566,19 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>STM32L476VC</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -69588,14 +69588,14 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>STM32L476QG</t>
+          <t>STM32L4A6QG</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -69610,14 +69610,14 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>STM32L476QG</t>
+          <t>STM32L4A6QG</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -69632,14 +69632,14 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>STM32L476QG</t>
+          <t>STM32L4A6QG</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -69654,14 +69654,14 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>STM32L496VE</t>
+          <t>STM32L4A6VG</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -69683,7 +69683,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>STM32L496VE</t>
+          <t>STM32L4A6VG</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -69705,7 +69705,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>STM32L496VE</t>
+          <t>STM32L4A6VG</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -69727,7 +69727,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>STM32L476VG</t>
+          <t>STM32L476VC</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -69749,7 +69749,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>STM32L476VG</t>
+          <t>STM32L476VC</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -69771,7 +69771,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>STM32L476VG</t>
+          <t>STM32L476VC</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -69793,7 +69793,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>STM32L496RE</t>
+          <t>STM32L4A6RG</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -69815,7 +69815,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>STM32L496RE</t>
+          <t>STM32L4A6RG</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -69837,7 +69837,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>STM32L496RE</t>
+          <t>STM32L4A6RG</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -69859,7 +69859,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>STM32L476RG</t>
+          <t>STM32L476QG</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -69881,7 +69881,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>STM32L476RG</t>
+          <t>STM32L476QG</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -69903,7 +69903,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>STM32L476RG</t>
+          <t>STM32L476QG</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -69925,7 +69925,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>STM32L496AE</t>
+          <t>STM32L496VE</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -69947,7 +69947,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>STM32L496AE</t>
+          <t>STM32L496VE</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -69969,7 +69969,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>STM32L496AE</t>
+          <t>STM32L496VE</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -69991,7 +69991,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>STM32L496ZE</t>
+          <t>STM32L476VG</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -70006,14 +70006,14 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>STM32L496ZE</t>
+          <t>STM32L476VG</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -70028,14 +70028,14 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>STM32L496ZE</t>
+          <t>STM32L476VG</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -70050,14 +70050,14 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>STM32L476ZE</t>
+          <t>STM32L496RE</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -70072,14 +70072,14 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>STM32L476ZE</t>
+          <t>STM32L496RE</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -70094,14 +70094,14 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>STM32L476ZE</t>
+          <t>STM32L496RE</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -70116,14 +70116,14 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>STM32L476ZG</t>
+          <t>STM32L476RG</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -70145,7 +70145,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>STM32L476ZG</t>
+          <t>STM32L476RG</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -70167,7 +70167,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>STM32L476ZG</t>
+          <t>STM32L476RG</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -70189,7 +70189,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>STM32L496VG</t>
+          <t>STM32L496AE</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -70211,7 +70211,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>STM32L496VG</t>
+          <t>STM32L496AE</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -70233,7 +70233,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>STM32L496VG</t>
+          <t>STM32L496AE</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -70255,7 +70255,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>STM32L496QG</t>
+          <t>STM32L496ZE</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -70277,7 +70277,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>STM32L496QG</t>
+          <t>STM32L496ZE</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -70299,7 +70299,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>STM32L496QG</t>
+          <t>STM32L496ZE</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -70321,7 +70321,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>STM32L476MG</t>
+          <t>STM32L476ZE</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -70343,7 +70343,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>STM32L476MG</t>
+          <t>STM32L476ZE</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -70365,7 +70365,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>STM32L476MG</t>
+          <t>STM32L476ZE</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -70387,7 +70387,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>STM32L496AG</t>
+          <t>STM32L476ZG</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -70402,14 +70402,14 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>STM32L496AG</t>
+          <t>STM32L476ZG</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -70424,14 +70424,14 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>STM32L496AG</t>
+          <t>STM32L476ZG</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -70446,14 +70446,14 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>STM32L476QE</t>
+          <t>STM32L496VG</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -70468,14 +70468,14 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>STM32L476QE</t>
+          <t>STM32L496VG</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -70490,14 +70490,14 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>STM32L476QE</t>
+          <t>STM32L496VG</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -70512,14 +70512,14 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>STM32L476VE</t>
+          <t>STM32L496QG</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -70534,14 +70534,14 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>STM32L476VE</t>
+          <t>STM32L496QG</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -70556,14 +70556,14 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>STM32L476VE</t>
+          <t>STM32L496QG</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -70578,14 +70578,14 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>STM32L476RE</t>
+          <t>STM32L476MG</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -70607,7 +70607,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>STM32L476RE</t>
+          <t>STM32L476MG</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -70629,7 +70629,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>STM32L476RE</t>
+          <t>STM32L476MG</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -70651,7 +70651,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>STM32L496RG</t>
+          <t>STM32L496AG</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -70673,7 +70673,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>STM32L496RG</t>
+          <t>STM32L496AG</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -70695,7 +70695,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>STM32L496RG</t>
+          <t>STM32L496AG</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -70717,7 +70717,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>STM32L496ZG</t>
+          <t>STM32L476QE</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -70732,14 +70732,14 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>STM32L496ZG</t>
+          <t>STM32L476QE</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -70754,14 +70754,14 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>STM32L496ZG</t>
+          <t>STM32L476QE</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -70776,14 +70776,14 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>STM32L476ME</t>
+          <t>STM32L476VE</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -70805,7 +70805,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>STM32L476ME</t>
+          <t>STM32L476VE</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -70827,7 +70827,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>STM32L476ME</t>
+          <t>STM32L476VE</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -70849,12 +70849,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L476RE</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -70864,19 +70864,19 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L476RE</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -70886,14 +70886,14 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L476RE</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -70915,12 +70915,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L496RG</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -70930,19 +70930,19 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>STM32L496WG</t>
+          <t>STM32L496RG</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -70959,12 +70959,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>STM32L496WG</t>
+          <t>STM32L496RG</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -70974,27 +70974,291 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
+          <t>STM32L496ZG</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>STM32L496ZG</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>STM32L496ZG</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>STM32L476ME</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>STM32L476ME</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>STM32L476ME</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L486xx family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Table 2. STM32L486xx family device features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Table 23. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 105 °C / -40 to 125 °C Junction temperature: -40 to 105 °C / -40 to 125 °C / -40 to 130 °C (datasheet offers 4 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
           <t>STM32L496WG</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr">
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>STM32L496WG</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>STM32L496WG</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
         <is>
           <t>Supply Voltage (V) min</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
         <is>
           <t>Table 22. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
         </is>

--- a/product_selector_out/STM32L4 series.xlsx
+++ b/product_selector_out/STM32L4 series.xlsx
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AM14" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN14" s="4" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="AM21" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN21" s="4" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="AM24" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN24" s="4" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="AM26" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN26" s="4" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM31" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN31" s="4" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="AM35" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN35" s="4" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="AM36" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN36" s="4" t="inlineStr">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="AM37" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN37" s="4" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="AM38" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN38" s="4" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="AM39" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN39" s="4" t="inlineStr">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="AM40" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN40" s="4" t="inlineStr">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="AM41" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN41" s="4" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="AM42" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN42" s="4" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="AM43" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN43" s="4" t="inlineStr">
@@ -16232,7 +16232,7 @@
       </c>
       <c r="AM58" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN58" s="4" t="inlineStr">
@@ -17213,7 +17213,7 @@
       </c>
       <c r="AM61" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN61" s="4" t="inlineStr">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="AM62" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN62" s="4" t="inlineStr">
@@ -18848,7 +18848,7 @@
       </c>
       <c r="AM66" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN66" s="4" t="inlineStr">
@@ -19175,7 +19175,7 @@
       </c>
       <c r="AM67" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN67" s="4" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="AM69" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN69" s="4" t="inlineStr">
@@ -20156,7 +20156,7 @@
       </c>
       <c r="AM70" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AN70" s="4" t="inlineStr">
@@ -33251,9 +33251,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN14" s="6" t="inlineStr">
@@ -33578,9 +33578,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr">
@@ -34886,9 +34886,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN19" s="6" t="inlineStr">
@@ -35213,9 +35213,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN20" s="6" t="inlineStr">
@@ -35540,9 +35540,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN21" s="6" t="inlineStr">
@@ -35867,9 +35867,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN22" s="6" t="inlineStr">
@@ -36194,9 +36194,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN23" s="6" t="inlineStr">
@@ -36521,9 +36521,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN24" s="6" t="inlineStr">
@@ -36848,9 +36848,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN25" s="6" t="inlineStr">
@@ -37175,9 +37175,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN26" s="6" t="inlineStr">
@@ -37829,9 +37829,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN28" s="6" t="inlineStr">
@@ -38810,9 +38810,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN31" s="6" t="inlineStr">
@@ -39137,9 +39137,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN32" s="6" t="inlineStr">
@@ -39464,9 +39464,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN33" s="6" t="inlineStr">
@@ -40118,9 +40118,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN35" s="6" t="inlineStr">
@@ -40445,9 +40445,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN36" s="6" t="inlineStr">
@@ -40772,9 +40772,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN37" s="6" t="inlineStr">
@@ -41099,9 +41099,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN38" s="6" t="inlineStr">
@@ -41426,9 +41426,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN39" s="6" t="inlineStr">
@@ -41753,9 +41753,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN40" s="6" t="inlineStr">
@@ -42080,9 +42080,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN41" s="6" t="inlineStr">
@@ -42407,9 +42407,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN42" s="6" t="inlineStr">
@@ -42734,9 +42734,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN43" s="6" t="inlineStr">
@@ -43061,9 +43061,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN44" s="6" t="inlineStr">
@@ -43388,9 +43388,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN45" s="6" t="inlineStr">
@@ -43715,9 +43715,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM46" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN46" s="6" t="inlineStr">
@@ -44042,9 +44042,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM47" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN47" s="6" t="inlineStr">
@@ -44369,9 +44369,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM48" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN48" s="6" t="inlineStr">
@@ -44696,9 +44696,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM49" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN49" s="6" t="inlineStr">
@@ -45023,9 +45023,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM50" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM50" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN50" s="6" t="inlineStr">
@@ -45350,9 +45350,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM51" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM51" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN51" s="6" t="inlineStr">
@@ -45677,9 +45677,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM52" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM52" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN52" s="6" t="inlineStr">
@@ -46004,9 +46004,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM53" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM53" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN53" s="6" t="inlineStr">
@@ -46331,9 +46331,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM54" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN54" s="6" t="inlineStr">
@@ -46658,9 +46658,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM55" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM55" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN55" s="6" t="inlineStr">
@@ -46985,9 +46985,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM56" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN56" s="6" t="inlineStr">
@@ -47312,9 +47312,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM57" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM57" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN57" s="6" t="inlineStr">
@@ -47639,9 +47639,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM58" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN58" s="6" t="inlineStr">
@@ -47966,9 +47966,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM59" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM59" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN59" s="6" t="inlineStr">
@@ -48293,9 +48293,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM60" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM60" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN60" s="6" t="inlineStr">
@@ -48620,9 +48620,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM61" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN61" s="6" t="inlineStr">
@@ -48947,9 +48947,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM62" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN62" s="6" t="inlineStr">
@@ -49274,9 +49274,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM63" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM63" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN63" s="6" t="inlineStr">
@@ -49601,9 +49601,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM64" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN64" s="6" t="inlineStr">
@@ -49928,9 +49928,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM65" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN65" s="6" t="inlineStr">
@@ -50255,9 +50255,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM66" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN66" s="6" t="inlineStr">
@@ -50582,9 +50582,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM67" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN67" s="6" t="inlineStr">
@@ -50909,9 +50909,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM68" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN68" s="6" t="inlineStr">
@@ -51236,9 +51236,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM69" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN69" s="6" t="inlineStr">
@@ -51563,9 +51563,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM70" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AM70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AN70" s="6" t="inlineStr">
@@ -52871,9 +52871,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM74" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN74" s="6" t="inlineStr">
@@ -53852,9 +53852,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM77" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM77" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN77" s="6" t="inlineStr">
@@ -54506,9 +54506,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM79" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN79" s="6" t="inlineStr">
@@ -54833,9 +54833,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM80" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM80" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN80" s="6" t="inlineStr">
@@ -62681,9 +62681,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM104" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM104" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN104" s="6" t="inlineStr">

--- a/product_selector_out/STM32L4 series.xlsx
+++ b/product_selector_out/STM32L4 series.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM105"/>
+  <dimension ref="A1:BN105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9609375" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l442kc.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l412c8.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l422cb.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l462ce.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l412c8.pdf</t>
         </is>
       </c>
@@ -2955,6 +2987,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l412c8.pdf</t>
         </is>
       </c>
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l412c8.pdf</t>
         </is>
       </c>
@@ -3609,6 +3651,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l462ce.pdf</t>
         </is>
       </c>
@@ -3936,6 +3983,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l452cc.pdf</t>
         </is>
       </c>
@@ -4263,6 +4315,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l432kb.pdf</t>
         </is>
       </c>
@@ -4590,6 +4647,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l452cc.pdf</t>
         </is>
       </c>
@@ -4917,6 +4979,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l462ce.pdf</t>
         </is>
       </c>
@@ -5244,6 +5311,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l422cb.pdf</t>
         </is>
       </c>
@@ -5571,6 +5643,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l452cc.pdf</t>
         </is>
       </c>
@@ -5898,6 +5975,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l422cb.pdf</t>
         </is>
       </c>
@@ -6225,6 +6307,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l412c8.pdf</t>
         </is>
       </c>
@@ -6552,6 +6639,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l452cc.pdf</t>
         </is>
       </c>
@@ -6879,6 +6971,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l412c8.pdf</t>
         </is>
       </c>
@@ -7206,6 +7303,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l412c8.pdf</t>
         </is>
       </c>
@@ -7533,6 +7635,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l432kb.pdf</t>
         </is>
       </c>
@@ -7860,6 +7967,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l452cc.pdf</t>
         </is>
       </c>
@@ -8187,6 +8299,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l452cc.pdf</t>
         </is>
       </c>
@@ -8514,6 +8631,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l412c8.pdf</t>
         </is>
       </c>
@@ -8841,6 +8963,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l422cb.pdf</t>
         </is>
       </c>
@@ -9168,6 +9295,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l443cc.pdf</t>
         </is>
       </c>
@@ -9495,6 +9627,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l443cc.pdf</t>
         </is>
       </c>
@@ -9822,6 +9959,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l433cb.pdf</t>
         </is>
       </c>
@@ -10149,6 +10291,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l433cb.pdf</t>
         </is>
       </c>
@@ -10476,6 +10623,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l433cb.pdf</t>
         </is>
       </c>
@@ -10803,6 +10955,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l443cc.pdf</t>
         </is>
       </c>
@@ -11130,6 +11287,11 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l433cb.pdf</t>
         </is>
       </c>
@@ -11457,6 +11619,11 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l433cb.pdf</t>
         </is>
       </c>
@@ -11784,6 +11951,11 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l475rc.pdf</t>
         </is>
       </c>
@@ -12111,6 +12283,11 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l475rc.pdf</t>
         </is>
       </c>
@@ -12438,6 +12615,11 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l475rc.pdf</t>
         </is>
       </c>
@@ -12765,6 +12947,11 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l475rc.pdf</t>
         </is>
       </c>
@@ -13092,6 +13279,11 @@
       </c>
       <c r="BM48" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l475rc.pdf</t>
         </is>
       </c>
@@ -13419,6 +13611,11 @@
       </c>
       <c r="BM49" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l475rc.pdf</t>
         </is>
       </c>
@@ -13746,6 +13943,11 @@
       </c>
       <c r="BM50" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l451cc.pdf</t>
         </is>
       </c>
@@ -14073,6 +14275,11 @@
       </c>
       <c r="BM51" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l471qe.pdf</t>
         </is>
       </c>
@@ -14400,6 +14607,11 @@
       </c>
       <c r="BM52" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l451cc.pdf</t>
         </is>
       </c>
@@ -14727,6 +14939,11 @@
       </c>
       <c r="BM53" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l471qe.pdf</t>
         </is>
       </c>
@@ -15054,6 +15271,11 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN54" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l471qe.pdf</t>
         </is>
       </c>
@@ -15381,6 +15603,11 @@
       </c>
       <c r="BM55" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l451cc.pdf</t>
         </is>
       </c>
@@ -15708,6 +15935,11 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN56" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l451cc.pdf</t>
         </is>
       </c>
@@ -16035,6 +16267,11 @@
       </c>
       <c r="BM57" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN57" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l471qe.pdf</t>
         </is>
       </c>
@@ -16362,6 +16599,11 @@
       </c>
       <c r="BM58" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN58" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l431cb.pdf</t>
         </is>
       </c>
@@ -16689,6 +16931,11 @@
       </c>
       <c r="BM59" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN59" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l451cc.pdf</t>
         </is>
       </c>
@@ -17016,6 +17263,11 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l471qe.pdf</t>
         </is>
       </c>
@@ -17343,6 +17595,11 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l431cb.pdf</t>
         </is>
       </c>
@@ -17670,6 +17927,11 @@
       </c>
       <c r="BM62" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN62" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l431cb.pdf</t>
         </is>
       </c>
@@ -17997,6 +18259,11 @@
       </c>
       <c r="BM63" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN63" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l451cc.pdf</t>
         </is>
       </c>
@@ -18324,6 +18591,11 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN64" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l471qe.pdf</t>
         </is>
       </c>
@@ -18651,6 +18923,11 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN65" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l471qe.pdf</t>
         </is>
       </c>
@@ -18978,6 +19255,11 @@
       </c>
       <c r="BM66" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN66" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l431cb.pdf</t>
         </is>
       </c>
@@ -19305,6 +19587,11 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN67" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l431cb.pdf</t>
         </is>
       </c>
@@ -19632,6 +19919,11 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN68" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l471qe.pdf</t>
         </is>
       </c>
@@ -19959,6 +20251,11 @@
       </c>
       <c r="BM69" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN69" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l431cb.pdf</t>
         </is>
       </c>
@@ -20286,6 +20583,11 @@
       </c>
       <c r="BM70" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN70" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l431cb.pdf</t>
         </is>
       </c>
@@ -20613,6 +20915,11 @@
       </c>
       <c r="BM71" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN71" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -20940,6 +21247,11 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN72" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -21267,6 +21579,11 @@
       </c>
       <c r="BM73" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN73" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
@@ -21594,6 +21911,11 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN74" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l486jg.pdf</t>
         </is>
       </c>
@@ -21921,6 +22243,11 @@
       </c>
       <c r="BM75" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN75" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
@@ -22248,6 +22575,11 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN76" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -22575,6 +22907,11 @@
       </c>
       <c r="BM77" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN77" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l486jg.pdf</t>
         </is>
       </c>
@@ -22902,6 +23239,11 @@
       </c>
       <c r="BM78" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN78" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -23229,6 +23571,11 @@
       </c>
       <c r="BM79" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN79" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l486jg.pdf</t>
         </is>
       </c>
@@ -23556,6 +23903,11 @@
       </c>
       <c r="BM80" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN80" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l486jg.pdf</t>
         </is>
       </c>
@@ -23883,6 +24235,11 @@
       </c>
       <c r="BM81" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN81" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
@@ -24210,6 +24567,11 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN82" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
@@ -24537,6 +24899,11 @@
       </c>
       <c r="BM83" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN83" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -24864,6 +25231,11 @@
       </c>
       <c r="BM84" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN84" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4a6ag.pdf</t>
         </is>
       </c>
@@ -25191,6 +25563,11 @@
       </c>
       <c r="BM85" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN85" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -25518,6 +25895,11 @@
       </c>
       <c r="BM86" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN86" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -25845,6 +26227,11 @@
       </c>
       <c r="BM87" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN87" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -26172,6 +26559,11 @@
       </c>
       <c r="BM88" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN88" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -26499,6 +26891,11 @@
       </c>
       <c r="BM89" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN89" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -26826,6 +27223,11 @@
       </c>
       <c r="BM90" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN90" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -27153,6 +27555,11 @@
       </c>
       <c r="BM91" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN91" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -27480,6 +27887,11 @@
       </c>
       <c r="BM92" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN92" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -27807,6 +28219,11 @@
       </c>
       <c r="BM93" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN93" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -28134,6 +28551,11 @@
       </c>
       <c r="BM94" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN94" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -28461,6 +28883,11 @@
       </c>
       <c r="BM95" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN95" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -28788,6 +29215,11 @@
       </c>
       <c r="BM96" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN96" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -29115,6 +29547,11 @@
       </c>
       <c r="BM97" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN97" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -29442,6 +29879,11 @@
       </c>
       <c r="BM98" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN98" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -29769,6 +30211,11 @@
       </c>
       <c r="BM99" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN99" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -30096,6 +30543,11 @@
       </c>
       <c r="BM100" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN100" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -30423,6 +30875,11 @@
       </c>
       <c r="BM101" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN101" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -30750,6 +31207,11 @@
       </c>
       <c r="BM102" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN102" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
@@ -31077,6 +31539,11 @@
       </c>
       <c r="BM103" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN103" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l476je.pdf</t>
         </is>
       </c>
@@ -31404,6 +31871,11 @@
       </c>
       <c r="BM104" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN104" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l486jg.pdf</t>
         </is>
       </c>
@@ -31731,12 +32203,17 @@
       </c>
       <c r="BM105" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN105" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l496ae.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -31757,16 +32234,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -31779,6 +32254,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -31798,7 +32274,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -31909,7 +32387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM105"/>
+  <dimension ref="A1:BN105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -31977,6 +32455,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32310,6 +32789,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -32405,6 +32889,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -32727,7 +33212,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33054,7 +33544,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33381,7 +33876,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33708,7 +34208,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34035,7 +34540,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34362,7 +34872,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34689,7 +35204,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35016,7 +35536,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35343,7 +35868,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35670,7 +36200,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35997,7 +36532,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36324,7 +36864,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36651,7 +37196,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36978,7 +37528,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37305,7 +37860,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37632,7 +38192,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37959,7 +38524,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38286,7 +38856,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38613,7 +39188,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38940,7 +39520,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39267,7 +39852,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39594,7 +40184,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39921,7 +40516,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40248,7 +40848,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40575,7 +41180,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40902,7 +41512,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41229,7 +41844,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41556,7 +42176,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41883,7 +42508,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42210,7 +42840,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42537,7 +43172,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42864,7 +43504,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
+      <c r="BM43" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43191,7 +43836,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43518,7 +44168,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
+      <c r="BM45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43845,7 +44500,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
+      <c r="BM46" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44172,7 +44832,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="6" t="inlineStr">
+      <c r="BM47" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44499,7 +45164,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM48" s="6" t="inlineStr">
+      <c r="BM48" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44826,7 +45496,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM49" s="6" t="inlineStr">
+      <c r="BM49" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45153,7 +45828,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM50" s="6" t="inlineStr">
+      <c r="BM50" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45480,7 +46160,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM51" s="6" t="inlineStr">
+      <c r="BM51" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45807,7 +46492,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM52" s="6" t="inlineStr">
+      <c r="BM52" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46134,7 +46824,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM53" s="6" t="inlineStr">
+      <c r="BM53" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46461,7 +47156,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="6" t="inlineStr">
+      <c r="BM54" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN54" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46788,7 +47488,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM55" s="6" t="inlineStr">
+      <c r="BM55" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47115,7 +47820,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="6" t="inlineStr">
+      <c r="BM56" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN56" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47442,7 +48152,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM57" s="6" t="inlineStr">
+      <c r="BM57" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN57" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47769,7 +48484,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM58" s="6" t="inlineStr">
+      <c r="BM58" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN58" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48096,7 +48816,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM59" s="6" t="inlineStr">
+      <c r="BM59" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN59" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48423,7 +49148,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="6" t="inlineStr">
+      <c r="BM60" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48750,7 +49480,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="6" t="inlineStr">
+      <c r="BM61" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49077,7 +49812,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM62" s="6" t="inlineStr">
+      <c r="BM62" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN62" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49404,7 +50144,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM63" s="6" t="inlineStr">
+      <c r="BM63" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN63" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49731,7 +50476,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM64" s="6" t="inlineStr">
+      <c r="BM64" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN64" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50058,7 +50808,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM65" s="6" t="inlineStr">
+      <c r="BM65" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN65" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50385,7 +51140,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM66" s="6" t="inlineStr">
+      <c r="BM66" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN66" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50712,7 +51472,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM67" s="6" t="inlineStr">
+      <c r="BM67" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN67" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51039,7 +51804,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="6" t="inlineStr">
+      <c r="BM68" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN68" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51366,7 +52136,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM69" s="6" t="inlineStr">
+      <c r="BM69" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN69" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51693,7 +52468,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM70" s="6" t="inlineStr">
+      <c r="BM70" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN70" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52020,7 +52800,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM71" s="6" t="inlineStr">
+      <c r="BM71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN71" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52347,7 +53132,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="6" t="inlineStr">
+      <c r="BM72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN72" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52674,7 +53464,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM73" s="6" t="inlineStr">
+      <c r="BM73" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN73" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53001,7 +53796,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM74" s="6" t="inlineStr">
+      <c r="BM74" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN74" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53328,7 +54128,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM75" s="6" t="inlineStr">
+      <c r="BM75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN75" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53655,7 +54460,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="6" t="inlineStr">
+      <c r="BM76" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN76" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53982,7 +54792,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM77" s="6" t="inlineStr">
+      <c r="BM77" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN77" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54309,7 +55124,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM78" s="6" t="inlineStr">
+      <c r="BM78" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN78" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54636,7 +55456,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM79" s="6" t="inlineStr">
+      <c r="BM79" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN79" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54963,7 +55788,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM80" s="6" t="inlineStr">
+      <c r="BM80" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN80" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55290,7 +56120,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM81" s="6" t="inlineStr">
+      <c r="BM81" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN81" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55617,7 +56452,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="6" t="inlineStr">
+      <c r="BM82" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN82" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55944,7 +56784,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM83" s="6" t="inlineStr">
+      <c r="BM83" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN83" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56271,7 +57116,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM84" s="6" t="inlineStr">
+      <c r="BM84" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN84" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56598,7 +57448,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM85" s="6" t="inlineStr">
+      <c r="BM85" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN85" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56925,7 +57780,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM86" s="6" t="inlineStr">
+      <c r="BM86" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN86" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57252,7 +58112,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM87" s="6" t="inlineStr">
+      <c r="BM87" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN87" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57579,7 +58444,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM88" s="6" t="inlineStr">
+      <c r="BM88" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN88" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57906,7 +58776,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM89" s="6" t="inlineStr">
+      <c r="BM89" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN89" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58233,7 +59108,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM90" s="6" t="inlineStr">
+      <c r="BM90" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN90" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58560,7 +59440,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM91" s="6" t="inlineStr">
+      <c r="BM91" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN91" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58887,7 +59772,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM92" s="6" t="inlineStr">
+      <c r="BM92" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN92" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -59214,7 +60104,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM93" s="6" t="inlineStr">
+      <c r="BM93" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN93" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -59541,7 +60436,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM94" s="6" t="inlineStr">
+      <c r="BM94" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN94" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -59868,7 +60768,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM95" s="6" t="inlineStr">
+      <c r="BM95" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN95" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -60195,7 +61100,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM96" s="6" t="inlineStr">
+      <c r="BM96" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN96" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -60522,7 +61432,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM97" s="6" t="inlineStr">
+      <c r="BM97" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN97" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -60849,7 +61764,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM98" s="6" t="inlineStr">
+      <c r="BM98" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN98" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -61176,7 +62096,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM99" s="6" t="inlineStr">
+      <c r="BM99" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN99" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -61503,7 +62428,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM100" s="6" t="inlineStr">
+      <c r="BM100" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN100" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -61830,7 +62760,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM101" s="6" t="inlineStr">
+      <c r="BM101" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN101" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -62157,7 +63092,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM102" s="6" t="inlineStr">
+      <c r="BM102" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN102" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -62484,7 +63424,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM103" s="6" t="inlineStr">
+      <c r="BM103" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN103" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -62811,7 +63756,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM104" s="6" t="inlineStr">
+      <c r="BM104" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN104" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -63138,7 +64088,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM105" s="6" t="inlineStr">
+      <c r="BM105" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN105" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -63146,8 +64101,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
